--- a/data/01_Corporate_Holdco/Consolidated_Trial_Balance_MANUAL.xlsx
+++ b/data/01_Corporate_Holdco/Consolidated_Trial_Balance_MANUAL.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB - Corporate" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB - Northbridge Software, Inc" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB - Verve Supply Co." sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TB - Northbridge Advisory Grou" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consolidated (unreviewed)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Known Issues" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TB - Corporate" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="TB - Northbridge Software, Inc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TB - Verve Supply Co." sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="TB - Northbridge Advisory Grou" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Consolidated (unreviewed)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Known Issues" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Built by Priya in Excel each month by re-typing balances off four different exports (QuickBooks Online, Xero, a spreadsheet, and this workbook itself). No consolidation software, no shared chart of accounts, no elimination entries. This is genuinely the entire close process for the group.</t>
+          <t>Built by Priya in Excel each month by re-typing balances off four different exports (NetSuite, Xero, a spreadsheet, and this workbook itself). No consolidation software, no shared chart of accounts, no elimination entries. This is genuinely the entire close process for the group.</t>
         </is>
       </c>
     </row>
@@ -1740,10 +1740,10 @@
         <v>3582109</v>
       </c>
       <c r="C3" t="n">
-        <v>2626605.87</v>
+        <v>2443112.87</v>
       </c>
       <c r="D3" t="n">
-        <v>955503.13</v>
+        <v>1138996.13</v>
       </c>
     </row>
     <row r="4">
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2609954</v>
+        <v>2426461</v>
       </c>
       <c r="C4" t="n">
         <v>3890556.8</v>
       </c>
       <c r="D4" t="n">
-        <v>-1280602.8</v>
+        <v>-1464095.8</v>
       </c>
     </row>
     <row r="5">
@@ -3565,10 +3565,10 @@
         <v>3582109</v>
       </c>
       <c r="D73" t="n">
-        <v>2626605.87</v>
+        <v>2443112.87</v>
       </c>
       <c r="E73" t="n">
-        <v>955503.13</v>
+        <v>1138996.13</v>
       </c>
     </row>
     <row r="74">
@@ -3583,13 +3583,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2609954</v>
+        <v>2426461</v>
       </c>
       <c r="D74" t="n">
         <v>3890556.8</v>
       </c>
       <c r="E74" t="n">
-        <v>-1280602.8</v>
+        <v>-1464095.8</v>
       </c>
     </row>
     <row r="75">
